--- a/documentos/modelo_dicionario_de_dados.xlsx
+++ b/documentos/modelo_dicionario_de_dados.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="99">
   <si>
     <t xml:space="preserve">MODELO DE DICIONÁRIO DE DADOS</t>
   </si>
@@ -75,6 +75,54 @@
     <t xml:space="preserve">Descrição / Regra de Negócio</t>
   </si>
   <si>
+    <t xml:space="preserve">funcionario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOINCREMENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chave primaria de identificação do funcionario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEXT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">campo de nome do funcionario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cliente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chave primaria de identificação do cliente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">campo de nome do cliente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">equipamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chave primaria de identificação do equipamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">campo de nome do equipamento</t>
+  </si>
+  <si>
     <t xml:space="preserve">INSTRUÇÕES E EXEMPLO PRÁTICO</t>
   </si>
   <si>
@@ -153,18 +201,9 @@
     <t xml:space="preserve">id_aluno</t>
   </si>
   <si>
-    <t xml:space="preserve">INT</t>
-  </si>
-  <si>
     <t xml:space="preserve">11</t>
   </si>
   <si>
-    <t xml:space="preserve">PK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NÃO</t>
-  </si>
-  <si>
     <t xml:space="preserve">AUTO_INCREMENT</t>
   </si>
   <si>
@@ -268,9 +307,6 @@
   </si>
   <si>
     <t xml:space="preserve">VARCHAR(255)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEXT</t>
   </si>
   <si>
     <t xml:space="preserve">DECIMAL(10,2)</t>
@@ -292,7 +328,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -359,6 +395,16 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Consolas"/>
+      <family val="0"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="13"/>
       <color rgb="FF1E3A8A"/>
@@ -436,72 +482,88 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -760,632 +822,704 @@
   <dimension ref="A1:I59"/>
   <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="45"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4"/>
+      <c r="B4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4"/>
+      <c r="B5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="9"/>
+      <c r="A10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="7"/>
+      <c r="I10" s="11" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="13"/>
+      <c r="A11" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="13"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="15" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="9"/>
+      <c r="A12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="7"/>
+      <c r="I12" s="11" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="13"/>
+      <c r="A13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="13"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="15" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="9"/>
+      <c r="A14" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="7"/>
+      <c r="I14" s="11" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="13"/>
+      <c r="A15" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="13"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="15" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="9"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="11"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="13"/>
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="15"/>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="9"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="11"/>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="13"/>
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="15"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="9"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="13"/>
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="15"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="9"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="11"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="13"/>
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="15"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="9"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="13"/>
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="15"/>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="9"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="11"/>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="13"/>
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="15"/>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="9"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="11"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="13"/>
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="15"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="9"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="11"/>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="13"/>
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="15"/>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="9"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="11"/>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="13"/>
+      <c r="A33" s="12"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="15"/>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="9"/>
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="11"/>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="13"/>
+      <c r="A35" s="12"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="15"/>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="9"/>
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="11"/>
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="13"/>
+      <c r="A37" s="12"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="15"/>
     </row>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="9"/>
+      <c r="A38" s="7"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="11"/>
     </row>
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="13"/>
+      <c r="A39" s="12"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="15"/>
     </row>
     <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="9"/>
+      <c r="A40" s="7"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="11"/>
     </row>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="10"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="13"/>
+      <c r="A41" s="12"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="15"/>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="9"/>
+      <c r="A42" s="7"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="11"/>
     </row>
     <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="10"/>
-      <c r="B43" s="10"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="13"/>
+      <c r="A43" s="12"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="15"/>
     </row>
     <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="9"/>
+      <c r="A44" s="7"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="11"/>
     </row>
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="10"/>
-      <c r="B45" s="10"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="13"/>
+      <c r="A45" s="12"/>
+      <c r="B45" s="12"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="12"/>
+      <c r="I45" s="15"/>
     </row>
     <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="9"/>
+      <c r="A46" s="7"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="11"/>
     </row>
     <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="10"/>
-      <c r="B47" s="10"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="13"/>
+      <c r="A47" s="12"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="15"/>
     </row>
     <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="6"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="9"/>
+      <c r="A48" s="7"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="11"/>
     </row>
     <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="10"/>
-      <c r="B49" s="10"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="13"/>
+      <c r="A49" s="12"/>
+      <c r="B49" s="12"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="13"/>
+      <c r="H49" s="12"/>
+      <c r="I49" s="15"/>
     </row>
     <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="9"/>
+      <c r="A50" s="7"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="11"/>
     </row>
     <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="10"/>
-      <c r="B51" s="10"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="13"/>
+      <c r="A51" s="12"/>
+      <c r="B51" s="12"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="12"/>
+      <c r="I51" s="15"/>
     </row>
     <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6"/>
-      <c r="B52" s="6"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="9"/>
+      <c r="A52" s="7"/>
+      <c r="B52" s="7"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="11"/>
     </row>
     <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="10"/>
-      <c r="B53" s="10"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="11"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="13"/>
+      <c r="A53" s="12"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="12"/>
+      <c r="I53" s="15"/>
     </row>
     <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="9"/>
+      <c r="A54" s="7"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="11"/>
     </row>
     <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="10"/>
-      <c r="B55" s="10"/>
-      <c r="C55" s="11"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="11"/>
-      <c r="H55" s="10"/>
-      <c r="I55" s="13"/>
+      <c r="A55" s="12"/>
+      <c r="B55" s="12"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="12"/>
+      <c r="I55" s="15"/>
     </row>
     <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="6"/>
-      <c r="B56" s="6"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="9"/>
+      <c r="A56" s="7"/>
+      <c r="B56" s="7"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="11"/>
     </row>
     <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="10"/>
-      <c r="B57" s="10"/>
-      <c r="C57" s="11"/>
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="11"/>
-      <c r="H57" s="10"/>
-      <c r="I57" s="13"/>
+      <c r="A57" s="12"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="12"/>
+      <c r="I57" s="15"/>
     </row>
     <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="6"/>
-      <c r="B58" s="6"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="9"/>
+      <c r="A58" s="7"/>
+      <c r="B58" s="7"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="11"/>
     </row>
     <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="10"/>
-      <c r="B59" s="10"/>
-      <c r="C59" s="11"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="12"/>
-      <c r="G59" s="11"/>
-      <c r="H59" s="10"/>
-      <c r="I59" s="13"/>
+      <c r="A59" s="12"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="13"/>
+      <c r="H59" s="12"/>
+      <c r="I59" s="15"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -1420,373 +1554,373 @@
   <dimension ref="A1:I25"/>
   <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="45"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>17</v>
+      <c r="A1" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>18</v>
+      <c r="A2" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="D17" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="14" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
+      <c r="F17" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>49</v>
+      <c r="G17" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>54</v>
+      <c r="A18" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>56</v>
+      <c r="A19" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="6" t="s">
+      <c r="A20" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H20" s="6" t="s">
+      <c r="B20" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="10" t="s">
+      <c r="E22" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C21" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F21" s="12" t="s">
+      <c r="H23" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G21" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="6" t="s">
+      <c r="I23" s="15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H22" s="6" t="s">
+      <c r="D24" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="I22" s="9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>72</v>
+      <c r="F24" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="G25" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>76</v>
+      <c r="A25" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1809,76 +1943,76 @@
   <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>61</v>
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>46</v>
+      <c r="A2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>79</v>
+      <c r="A3" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>53</v>
+      <c r="A4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>81</v>
+      <c r="A5" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>82</v>
+      <c r="A6" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>83</v>
+      <c r="A7" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>58</v>
+      <c r="A8" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>84</v>
+      <c r="A9" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>85</v>
+      <c r="A10" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>86</v>
+      <c r="A11" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/documentos/modelo_dicionario_de_dados.xlsx
+++ b/documentos/modelo_dicionario_de_dados.xlsx
@@ -12,6 +12,9 @@
     <sheet name="Instruções e Exemplo" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Validações" sheetId="3" state="hidden" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Dicionário de Dados'!$A$9:$I$53</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -22,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="151">
   <si>
     <t xml:space="preserve">MODELO DE DICIONÁRIO DE DADOS</t>
   </si>
@@ -105,6 +108,52 @@
     <t xml:space="preserve">campo de nome do funcionario</t>
   </si>
   <si>
+    <t xml:space="preserve">id_cargo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIQUE(id,id_cargo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cargo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chave estrangeira de identificação do cargo do funcionario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">status</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">status do fucionario</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve"> (0,1)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">data_cadastro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">datetime(‘now’,’localtime’)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data cadastro do funcionario</t>
+  </si>
+  <si>
     <t xml:space="preserve">cliente</t>
   </si>
   <si>
@@ -114,6 +163,43 @@
     <t xml:space="preserve">campo de nome do cliente</t>
   </si>
   <si>
+    <t xml:space="preserve">telefone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIQUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">telefone do cliente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e-mail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e-mail do cliente</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">status do cliente</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve"> (0,1)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">data cadastro do cliente</t>
+  </si>
+  <si>
     <t xml:space="preserve">equipamento</t>
   </si>
   <si>
@@ -123,6 +209,178 @@
     <t xml:space="preserve">campo de nome do equipamento</t>
   </si>
   <si>
+    <t xml:space="preserve">id_marca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIQUE(id,id_marca)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chave estrangeira de identificação da marca do equipamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_modelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIQUE(id,id_modelo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">modelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chave estrangeira de identificação do modelo do equipamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_tipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIQUE(id,id_tipo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chave estrangeira de identificação do tipo do equipamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">serial_number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">imei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_cliente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIQUE(id,id_cliente)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chave estrangeira de identificação do cliente dono do equipamento</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">status do equipamento </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">(0,1)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">data cadastro do equipamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">situacao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chave primaria de identificação da situacao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">campo de nome da situacao</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">status da situacao </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">(0,1)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">data cadastro da situacao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chave primaria de identificação do cargo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">campo de nome do cargo</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">status do cargo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve"> (0,1)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">data cadastro do cargo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chave primaria de identificação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">campo de nome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_funcionario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIQUE(id,id_funcionario)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chave estrangeira de identificação do funcionario </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">status</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve"> (0,1)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">data cadastro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">status (0,1)</t>
+  </si>
+  <si>
     <t xml:space="preserve">INSTRUÇÕES E EXEMPLO PRÁTICO</t>
   </si>
   <si>
@@ -256,9 +514,6 @@
   </si>
   <si>
     <t xml:space="preserve">id_turma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FK</t>
   </si>
   <si>
     <t xml:space="preserve">tb_turmas(id_turma)</t>
@@ -413,7 +668,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -424,6 +679,54 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1E3A8A"/>
         <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4C7DC"/>
+        <bgColor rgb="FFCBD5E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD7D7"/>
+        <bgColor rgb="FFFFD8CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEDCE6"/>
+        <bgColor rgb="FFCBD5E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF5CE"/>
+        <bgColor rgb="FFF6F9D4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFD095"/>
+        <bgColor rgb="FFB4C7DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD8CE"/>
+        <bgColor rgb="FFFFD7D7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9D4"/>
+        <bgColor rgb="FFFFF5CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0C2CD"/>
+        <bgColor rgb="FFCBD5E1"/>
       </patternFill>
     </fill>
     <fill>
@@ -482,7 +785,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="62">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -523,14 +826,170 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -547,11 +1006,19 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -576,6 +1043,95 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="11">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1E3A8A"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFAFD095"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB4C7DC"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDEDCE6"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE0C2CD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F9D4"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFD7D7"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFD8CE"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF5CE"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -592,12 +1148,12 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FFB4C7DC"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFF6F9D4"/>
       <rgbColor rgb="FFF8FAFC"/>
-      <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -611,13 +1167,13 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFDEDCE6"/>
+      <rgbColor rgb="FFFFD7D7"/>
+      <rgbColor rgb="FFFFF5CE"/>
+      <rgbColor rgb="FFAFD095"/>
+      <rgbColor rgb="FFE0C2CD"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFFD8CE"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -637,6 +1193,10 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -819,7 +1379,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I1048576"/>
   <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
@@ -827,7 +1387,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="35.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="45"/>
   </cols>
@@ -842,6 +1402,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3" customFormat="false" ht="8.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>2</v>
@@ -870,6 +1431,7 @@
         <v>7</v>
       </c>
     </row>
+    <row r="8" customFormat="false" ht="7.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
         <v>8</v>
@@ -916,622 +1478,1212 @@
       <c r="F10" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="8" t="s">
         <v>22</v>
       </c>
       <c r="H10" s="7"/>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="10" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="15" t="s">
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="8"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="10" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>27</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>18</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="11" t="s">
-        <v>28</v>
+      <c r="G12" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="7"/>
+      <c r="I13" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" s="7"/>
+      <c r="I14" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C16" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" s="13"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="s">
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" s="12"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H17" s="11"/>
+      <c r="I17" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H18" s="11"/>
+      <c r="I18" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="11"/>
+      <c r="I19" s="14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H20" s="11"/>
+      <c r="I20" s="14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" s="15"/>
+      <c r="I21" s="18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="16"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="I23" s="18" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="I24" s="18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="I25" s="18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" s="16"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="18"/>
+    </row>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" s="16"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="18"/>
+    </row>
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="I28" s="18" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15"/>
+      <c r="I29" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H30" s="15"/>
+      <c r="I30" s="18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F31" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="H31" s="20"/>
+      <c r="I31" s="23" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" s="21"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="20"/>
+      <c r="I33" s="23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="H34" s="20"/>
+      <c r="I34" s="23" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B35" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C35" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9" t="s">
+      <c r="D35" s="27"/>
+      <c r="E35" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" s="10" t="s">
+      <c r="F35" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="17" t="s">
+      <c r="H35" s="25"/>
+      <c r="I35" s="28" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B36" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C36" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="15" t="s">
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="H36" s="25"/>
+      <c r="I36" s="28" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" s="25" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="11"/>
-    </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="15"/>
-    </row>
-    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="11"/>
-    </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="15"/>
-    </row>
-    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="11"/>
-    </row>
-    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="15"/>
-    </row>
-    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="11"/>
-    </row>
-    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="15"/>
-    </row>
-    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="11"/>
-    </row>
-    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="15"/>
-    </row>
-    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="11"/>
-    </row>
-    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="15"/>
-    </row>
-    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="11"/>
-    </row>
-    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="15"/>
-    </row>
-    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="11"/>
-    </row>
-    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="15"/>
-    </row>
-    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="11"/>
-    </row>
-    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="15"/>
-    </row>
-    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="11"/>
-    </row>
-    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="12"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="15"/>
-    </row>
-    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="11"/>
-    </row>
-    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="12"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="15"/>
+      <c r="C37" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="25"/>
+      <c r="I37" s="28" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="11"/>
-    </row>
-    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="12"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="15"/>
-    </row>
-    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="11"/>
-    </row>
-    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="12"/>
-      <c r="B41" s="12"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="15"/>
-    </row>
-    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="7"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="11"/>
-    </row>
-    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="12"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="15"/>
-    </row>
-    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="11"/>
-    </row>
-    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="12"/>
-      <c r="B45" s="12"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="12"/>
-      <c r="I45" s="15"/>
-    </row>
-    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="7"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="11"/>
-    </row>
-    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="12"/>
-      <c r="B47" s="12"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="12"/>
-      <c r="I47" s="15"/>
-    </row>
-    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7"/>
-      <c r="B48" s="7"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="7"/>
-      <c r="I48" s="11"/>
-    </row>
-    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="12"/>
-      <c r="B49" s="12"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="12"/>
-      <c r="I49" s="15"/>
-    </row>
-    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="8"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="11"/>
-    </row>
-    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="12"/>
-      <c r="B51" s="12"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="12"/>
-      <c r="I51" s="15"/>
-    </row>
-    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7"/>
-      <c r="B52" s="7"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="8"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="11"/>
-    </row>
-    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="12"/>
-      <c r="B53" s="12"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="12"/>
-      <c r="I53" s="15"/>
+      <c r="A38" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="G38" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="H38" s="25"/>
+      <c r="I38" s="28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39" s="34" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="F39" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G39" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="H39" s="30"/>
+      <c r="I39" s="33" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" s="34" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="H40" s="30"/>
+      <c r="I40" s="33" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" s="34" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="C41" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="32"/>
+      <c r="E41" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="F41" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G41" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="H41" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" s="35" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" s="34" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G42" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="30"/>
+      <c r="I42" s="33" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" s="34" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G43" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="H43" s="30"/>
+      <c r="I43" s="33" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" s="41" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B44" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" s="39"/>
+      <c r="E44" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="F44" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="G44" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="H44" s="37"/>
+      <c r="I44" s="40" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="45" s="41" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B45" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="D45" s="39"/>
+      <c r="E45" s="39"/>
+      <c r="F45" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="G45" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="H45" s="37"/>
+      <c r="I45" s="40" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="46" s="41" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B46" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="C46" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" s="39"/>
+      <c r="E46" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="F46" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="G46" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="H46" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" s="42" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" s="41" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B47" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="C47" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" s="39"/>
+      <c r="E47" s="39"/>
+      <c r="F47" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="G47" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="37"/>
+      <c r="I47" s="40" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="48" s="41" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B48" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="C48" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="D48" s="39"/>
+      <c r="E48" s="39"/>
+      <c r="F48" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="G48" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="H48" s="37"/>
+      <c r="I48" s="40" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="49" s="48" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" s="46"/>
+      <c r="E49" s="46" t="s">
+        <v>20</v>
+      </c>
+      <c r="F49" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="G49" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="H49" s="44"/>
+      <c r="I49" s="47" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="50" s="48" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="D50" s="46"/>
+      <c r="E50" s="46"/>
+      <c r="F50" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="G50" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="H50" s="44"/>
+      <c r="I50" s="47" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51" s="48" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="C51" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" s="46"/>
+      <c r="E51" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="F51" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="G51" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="H51" s="44" t="s">
+        <v>17</v>
+      </c>
+      <c r="I51" s="49" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="52" s="48" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" s="44" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" s="46"/>
+      <c r="E52" s="46"/>
+      <c r="F52" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="G52" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="44"/>
+      <c r="I52" s="47" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" s="48" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B53" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="C53" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="D53" s="46"/>
+      <c r="E53" s="46"/>
+      <c r="F53" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="G53" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="H53" s="44"/>
+      <c r="I53" s="47" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="11"/>
+      <c r="A54" s="51"/>
+      <c r="B54" s="51"/>
+      <c r="C54" s="52"/>
+      <c r="D54" s="53"/>
+      <c r="E54" s="53"/>
+      <c r="F54" s="53"/>
+      <c r="G54" s="52"/>
+      <c r="H54" s="51"/>
+      <c r="I54" s="54"/>
     </row>
     <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="12"/>
-      <c r="B55" s="12"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="15"/>
+      <c r="A55" s="55"/>
+      <c r="B55" s="55"/>
+      <c r="C55" s="56"/>
+      <c r="D55" s="57"/>
+      <c r="E55" s="57"/>
+      <c r="F55" s="57"/>
+      <c r="G55" s="56"/>
+      <c r="H55" s="55"/>
+      <c r="I55" s="58"/>
     </row>
     <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="7"/>
-      <c r="B56" s="7"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="11"/>
+      <c r="A56" s="51"/>
+      <c r="B56" s="51"/>
+      <c r="C56" s="52"/>
+      <c r="D56" s="53"/>
+      <c r="E56" s="53"/>
+      <c r="F56" s="53"/>
+      <c r="G56" s="52"/>
+      <c r="H56" s="51"/>
+      <c r="I56" s="54"/>
     </row>
     <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="12"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="15"/>
+      <c r="A57" s="55"/>
+      <c r="B57" s="55"/>
+      <c r="C57" s="56"/>
+      <c r="D57" s="57"/>
+      <c r="E57" s="57"/>
+      <c r="F57" s="57"/>
+      <c r="G57" s="56"/>
+      <c r="H57" s="55"/>
+      <c r="I57" s="58"/>
     </row>
     <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="7"/>
-      <c r="B58" s="7"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="11"/>
+      <c r="A58" s="51"/>
+      <c r="B58" s="51"/>
+      <c r="C58" s="52"/>
+      <c r="D58" s="53"/>
+      <c r="E58" s="53"/>
+      <c r="F58" s="53"/>
+      <c r="G58" s="52"/>
+      <c r="H58" s="51"/>
+      <c r="I58" s="54"/>
     </row>
     <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="12"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="13"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="12"/>
-      <c r="I59" s="15"/>
-    </row>
+      <c r="A59" s="55"/>
+      <c r="B59" s="55"/>
+      <c r="C59" s="56"/>
+      <c r="D59" s="57"/>
+      <c r="E59" s="57"/>
+      <c r="F59" s="57"/>
+      <c r="G59" s="56"/>
+      <c r="H59" s="55"/>
+      <c r="I59" s="58"/>
+    </row>
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="51"/>
+      <c r="B60" s="51"/>
+      <c r="C60" s="52"/>
+      <c r="D60" s="53"/>
+      <c r="E60" s="53"/>
+      <c r="F60" s="53"/>
+      <c r="G60" s="52"/>
+      <c r="H60" s="51"/>
+      <c r="I60" s="54"/>
+    </row>
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="55"/>
+      <c r="B61" s="55"/>
+      <c r="C61" s="56"/>
+      <c r="D61" s="57"/>
+      <c r="E61" s="57"/>
+      <c r="F61" s="57"/>
+      <c r="G61" s="56"/>
+      <c r="H61" s="55"/>
+      <c r="I61" s="58"/>
+    </row>
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="51"/>
+      <c r="B62" s="51"/>
+      <c r="C62" s="52"/>
+      <c r="D62" s="53"/>
+      <c r="E62" s="53"/>
+      <c r="F62" s="53"/>
+      <c r="G62" s="52"/>
+      <c r="H62" s="51"/>
+      <c r="I62" s="54"/>
+    </row>
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="55"/>
+      <c r="B63" s="55"/>
+      <c r="C63" s="56"/>
+      <c r="D63" s="57"/>
+      <c r="E63" s="57"/>
+      <c r="F63" s="57"/>
+      <c r="G63" s="56"/>
+      <c r="H63" s="55"/>
+      <c r="I63" s="58"/>
+    </row>
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="51"/>
+      <c r="B64" s="51"/>
+      <c r="C64" s="52"/>
+      <c r="D64" s="53"/>
+      <c r="E64" s="53"/>
+      <c r="F64" s="53"/>
+      <c r="G64" s="52"/>
+      <c r="H64" s="51"/>
+      <c r="I64" s="54"/>
+    </row>
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="55"/>
+      <c r="B65" s="55"/>
+      <c r="C65" s="56"/>
+      <c r="D65" s="57"/>
+      <c r="E65" s="57"/>
+      <c r="F65" s="57"/>
+      <c r="G65" s="56"/>
+      <c r="H65" s="55"/>
+      <c r="I65" s="58"/>
+    </row>
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="51"/>
+      <c r="B66" s="51"/>
+      <c r="C66" s="52"/>
+      <c r="D66" s="53"/>
+      <c r="E66" s="53"/>
+      <c r="F66" s="53"/>
+      <c r="G66" s="52"/>
+      <c r="H66" s="51"/>
+      <c r="I66" s="54"/>
+    </row>
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="55"/>
+      <c r="B67" s="55"/>
+      <c r="C67" s="56"/>
+      <c r="D67" s="57"/>
+      <c r="E67" s="57"/>
+      <c r="F67" s="57"/>
+      <c r="G67" s="56"/>
+      <c r="H67" s="55"/>
+      <c r="I67" s="58"/>
+    </row>
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="51"/>
+      <c r="B68" s="51"/>
+      <c r="C68" s="52"/>
+      <c r="D68" s="53"/>
+      <c r="E68" s="53"/>
+      <c r="F68" s="53"/>
+      <c r="G68" s="52"/>
+      <c r="H68" s="51"/>
+      <c r="I68" s="54"/>
+    </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
+  <autoFilter ref="A9:I53"/>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C10:C59" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C10:C68" type="list">
       <formula1>Validações!$A$1:$A$11</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E10:E59" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E10:E68" type="list">
       <formula1>Validações!$B$1:$B$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F10:F59" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F10:F68" type="list">
       <formula1>Validações!$C$1:$C$2</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1543,6 +2695,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1566,89 +2719,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>36</v>
+      <c r="A4" s="59" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="60" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>38</v>
+      <c r="A5" s="59" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="60" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>40</v>
+      <c r="A6" s="59" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="60" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>42</v>
+      <c r="A7" s="59" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="60" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>44</v>
+      <c r="A8" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" s="60" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>46</v>
+      <c r="A9" s="59" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" s="60" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>48</v>
+      <c r="A10" s="59" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="60" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>50</v>
+      <c r="A11" s="59" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="60" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>52</v>
+      <c r="A12" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="60" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="20" t="s">
-        <v>53</v>
+      <c r="A14" s="61" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1656,7 +2809,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>10</v>
@@ -1671,256 +2824,256 @@
         <v>13</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>55</v>
+        <v>108</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>56</v>
+        <v>109</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="13" t="s">
+      <c r="A17" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="B17" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="C17" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="14" t="s">
+      <c r="D17" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="E17" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="I17" s="15" t="s">
-        <v>62</v>
+      <c r="F17" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="52" t="s">
+        <v>113</v>
+      </c>
+      <c r="H17" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="54" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>67</v>
+      <c r="A18" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="B18" s="55" t="s">
+        <v>116</v>
+      </c>
+      <c r="C18" s="56" t="s">
+        <v>117</v>
+      </c>
+      <c r="D18" s="57" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" s="57" t="s">
+        <v>119</v>
+      </c>
+      <c r="F18" s="57" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="56" t="s">
+        <v>114</v>
+      </c>
+      <c r="H18" s="55" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="H19" s="12" t="s">
-        <v>69</v>
+      <c r="A19" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="C19" s="52" t="s">
+        <v>117</v>
+      </c>
+      <c r="D19" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="F19" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="H19" s="51" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>72</v>
+      <c r="A20" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="57" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" s="57" t="s">
+        <v>119</v>
+      </c>
+      <c r="F20" s="57" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" s="56" t="s">
+        <v>114</v>
+      </c>
+      <c r="H20" s="55" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="F21" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="G21" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="H21" s="12" t="s">
-        <v>76</v>
+      <c r="A21" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" s="51" t="s">
+        <v>126</v>
+      </c>
+      <c r="C21" s="52" t="s">
+        <v>117</v>
+      </c>
+      <c r="D21" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="E21" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="F21" s="53" t="s">
+        <v>127</v>
+      </c>
+      <c r="G21" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="H21" s="51" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" s="8" t="s">
+      <c r="A22" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="B22" s="55" t="s">
+        <v>130</v>
+      </c>
+      <c r="C22" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>80</v>
+      <c r="D22" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="E22" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" s="57" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="56" t="s">
+        <v>114</v>
+      </c>
+      <c r="H22" s="55" t="s">
+        <v>131</v>
+      </c>
+      <c r="I22" s="58" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" s="13" t="s">
+      <c r="A23" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="B23" s="51" t="s">
+        <v>130</v>
+      </c>
+      <c r="C23" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" s="14" t="s">
+      <c r="D23" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="E23" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="F23" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="H23" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="I23" s="15" t="s">
-        <v>82</v>
+      <c r="F23" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="52" t="s">
+        <v>113</v>
+      </c>
+      <c r="H23" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="I23" s="54" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>85</v>
+      <c r="A24" s="55" t="s">
+        <v>133</v>
+      </c>
+      <c r="B24" s="55" t="s">
+        <v>135</v>
+      </c>
+      <c r="C24" s="56" t="s">
+        <v>117</v>
+      </c>
+      <c r="D24" s="57" t="s">
+        <v>136</v>
+      </c>
+      <c r="E24" s="57" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="57" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24" s="56" t="s">
+        <v>114</v>
+      </c>
+      <c r="H24" s="55" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" s="13" t="s">
+      <c r="A25" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="B25" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="C25" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>89</v>
+      <c r="D25" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="E25" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="F25" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" s="52" t="s">
+        <v>140</v>
+      </c>
+      <c r="H25" s="51" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -1950,15 +3103,15 @@
         <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>21</v>
@@ -1966,23 +3119,23 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>66</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1992,27 +3145,27 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>96</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
